--- a/법령_개정안_안내/database/법규리스트.xlsx
+++ b/법령_개정안_안내/database/법규리스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Windows\Python\notebooks\법령_개정안_안내\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E29A03-59F5-4864-947E-A5E6E492481A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F541D904-E9AA-4633-8A51-DBB3F8C08696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="288">
   <si>
     <t>법령명</t>
   </si>
@@ -559,6 +559,9 @@
   </si>
   <si>
     <t>중소기업창업지원법시행령</t>
+  </si>
+  <si>
+    <t>20260901</t>
   </si>
   <si>
     <t>중소기업창업지원법시행규칙</t>
@@ -2347,37 +2350,37 @@
         <v>177</v>
       </c>
       <c r="B99" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
       <c r="C99" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B100" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C100" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B101" t="s">
         <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B102" t="s">
         <v>151</v>
@@ -2388,18 +2391,18 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B103" t="s">
         <v>8</v>
       </c>
       <c r="C103" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B104" t="s">
         <v>28</v>
@@ -2410,73 +2413,73 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B105" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C105" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B106" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C106" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B107" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C107" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B108" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C108" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B109" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C109" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B110" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C110" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B111" t="s">
         <v>57</v>
@@ -2487,7 +2490,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B112" t="s">
         <v>8</v>
@@ -2498,84 +2501,84 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B113" t="s">
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B114" t="s">
         <v>8</v>
       </c>
       <c r="C114" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B115" t="s">
         <v>8</v>
       </c>
       <c r="C115" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B116" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C116" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B117" t="s">
         <v>8</v>
       </c>
       <c r="C117" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B118" t="s">
         <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B119" t="s">
         <v>8</v>
       </c>
       <c r="C119" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B120" t="s">
         <v>137</v>
@@ -2586,40 +2589,40 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B121" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C121" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B122" t="s">
         <v>8</v>
       </c>
       <c r="C122" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B123" t="s">
         <v>8</v>
       </c>
       <c r="C123" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B124" t="s">
         <v>57</v>
@@ -2630,18 +2633,18 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B125" t="s">
         <v>8</v>
       </c>
       <c r="C125" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B126" t="s">
         <v>57</v>
@@ -2652,18 +2655,18 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B127" t="s">
         <v>8</v>
       </c>
       <c r="C127" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B128" t="s">
         <v>92</v>
@@ -2674,7 +2677,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B129" t="s">
         <v>92</v>
@@ -2685,7 +2688,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B130" t="s">
         <v>92</v>
@@ -2696,7 +2699,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B131" t="s">
         <v>100</v>
@@ -2707,117 +2710,117 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B132" t="s">
         <v>8</v>
       </c>
       <c r="C132" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B133" t="s">
         <v>8</v>
       </c>
       <c r="C133" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B134" t="s">
         <v>8</v>
       </c>
       <c r="C134" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B135" t="s">
         <v>8</v>
       </c>
       <c r="C135" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B136" t="s">
         <v>8</v>
       </c>
       <c r="C136" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B137" t="s">
         <v>8</v>
       </c>
       <c r="C137" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B138" t="s">
         <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B139" t="s">
         <v>8</v>
       </c>
       <c r="C139" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B140" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C140" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B141" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C141" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B142" t="s">
         <v>87</v>
@@ -2828,7 +2831,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B143" t="s">
         <v>171</v>
@@ -2839,62 +2842,62 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B144" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C144" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B145" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C145" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B146" t="s">
         <v>8</v>
       </c>
       <c r="C146" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B147" t="s">
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B148" t="s">
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B149" t="s">
         <v>171</v>
@@ -2905,120 +2908,120 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B150" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C150" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B151" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C151" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B152" t="s">
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B153" t="s">
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B154" t="s">
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B155" t="s">
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B156" t="s">
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B157" t="s">
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B158" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C158" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B159" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C159" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>280</v>
+      </c>
+      <c r="B160" t="s">
         <v>279</v>
-      </c>
-      <c r="B160" t="s">
-        <v>278</v>
       </c>
       <c r="C160" t="s">
         <v>73</v>
@@ -3026,18 +3029,18 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B161" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C161" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B162" t="s">
         <v>92</v>
@@ -3048,24 +3051,24 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B163" t="s">
         <v>155</v>
       </c>
       <c r="C163" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B164" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C164" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
